--- a/AlarmProcessor/alarms.xlsx
+++ b/AlarmProcessor/alarms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/whuaning/Git/AutoOps/AlarmProcessor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FECFA8-81CE-0943-A4C9-7CB28B0DAC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E83C96-DC56-3E47-9028-FADEED041CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="27620" windowHeight="17040" xr2:uid="{EFA5CA1F-2FCE-F944-B84C-F49CCED66540}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="178">
   <si>
     <t>考虑将更大的实例类型用于您的专用主节点。由于其在集群稳定性和蓝/绿部署中的作用，专用主节点的 CPU 使用率应比数据节点低。</t>
   </si>
@@ -431,21 +431,6 @@
   </si>
   <si>
     <t>向 Amazon S3 存储桶提出的 HTTP 请求（不论类型如何）的总数。如果您要将某个指标配置用于某个筛选调节，那么该指标将仅返回符合该筛选条件要求的 HTTP 请求。</t>
-  </si>
-  <si>
-    <t>AWS/S4</t>
-  </si>
-  <si>
-    <t>AWS/S5</t>
-  </si>
-  <si>
-    <t>AWS/S6</t>
-  </si>
-  <si>
-    <t>AWS/S7</t>
-  </si>
-  <si>
-    <t>AWS/S8</t>
   </si>
   <si>
     <t>CpuSystem+CpuUser</t>
@@ -989,10 +974,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -1018,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1052,7 +1037,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1213,7 +1198,7 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D11">
         <v>60</v>
@@ -1222,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
@@ -1236,7 +1221,7 @@
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D12">
         <v>60</v>
@@ -1245,10 +1230,10 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" hidden="1" x14ac:dyDescent="0.2">
@@ -1271,7 +1256,7 @@
         <v>79</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1294,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1317,7 +1302,7 @@
         <v>79</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1331,7 +1316,7 @@
         <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1345,7 +1330,7 @@
         <v>80</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1359,7 +1344,7 @@
         <v>81</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1373,7 +1358,7 @@
         <v>82</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1387,7 +1372,7 @@
         <v>83</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1398,10 +1383,10 @@
         <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -1412,7 +1397,7 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D22">
         <v>60</v>
@@ -1422,7 +1407,7 @@
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1445,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1459,7 +1444,7 @@
         <v>84</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1473,7 +1458,7 @@
         <v>85</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1487,7 +1472,7 @@
         <v>86</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1501,7 +1486,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1515,7 +1500,7 @@
         <v>81</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1529,7 +1514,7 @@
         <v>88</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1566,7 +1551,7 @@
         <v>92</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1603,7 +1588,7 @@
         <v>93</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1637,7 +1622,7 @@
         <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D35">
         <v>300</v>
@@ -1646,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>78</v>
@@ -1686,7 +1671,7 @@
         <v>98</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1746,7 +1731,7 @@
         <v>101</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="119" x14ac:dyDescent="0.2">
@@ -1829,7 +1814,7 @@
         <v>106</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="34" x14ac:dyDescent="0.2">
@@ -1852,7 +1837,7 @@
         <v>111</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -1866,7 +1851,7 @@
         <v>110</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2046,7 +2031,7 @@
         <v>14</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2269,7 +2254,7 @@
         <v>118</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
         <v>121</v>
@@ -2283,7 +2268,7 @@
         <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
         <v>122</v>
@@ -2295,7 +2280,7 @@
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>129</v>
@@ -2306,7 +2291,7 @@
         <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
         <v>123</v>
@@ -2320,7 +2305,7 @@
         <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
         <v>124</v>
@@ -2334,7 +2319,7 @@
         <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
         <v>125</v>
@@ -2345,13 +2330,13 @@
     </row>
     <row r="71" spans="1:7" ht="221" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D71">
         <v>300</v>
@@ -2363,18 +2348,18 @@
         <v>60</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" t="s">
         <v>140</v>
-      </c>
-      <c r="C72" t="s">
-        <v>145</v>
       </c>
       <c r="D72">
         <v>300</v>
@@ -2391,13 +2376,13 @@
     </row>
     <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D73">
         <v>60</v>
@@ -2409,32 +2394,32 @@
         <v>85</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C74" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D75">
         <v>60</v>
@@ -2443,21 +2428,21 @@
         <v>3</v>
       </c>
       <c r="F75" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D76">
         <v>60</v>
@@ -2466,10 +2451,10 @@
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -2477,24 +2462,24 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G78" s="3"/>
     </row>
     <row r="79" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
